--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119624335</v>
+        <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>90801</v>
+        <v>96792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>655</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,21 +715,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 765, Ankarsrum, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579317</v>
+        <v>579214</v>
       </c>
       <c r="R2" t="n">
-        <v>6398111</v>
+        <v>6398230</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,12 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,16 +789,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624335</t>
+          <t>https://artportalen.se/Sighting/137091341</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119266053</v>
+        <v>119624335</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>90801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>655</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,21 +830,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>A 765, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579195</v>
+        <v>579317</v>
       </c>
       <c r="R3" t="n">
-        <v>6398252</v>
+        <v>6398111</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,51 +903,62 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119266053</t>
+          <t>https://artportalen.se/Sighting/119624335</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131734488</v>
+        <v>119266053</v>
       </c>
       <c r="B4" t="n">
-        <v>96410</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2812</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kärren Sydväst, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579272</v>
+        <v>579195</v>
       </c>
       <c r="R4" t="n">
-        <v>6398140</v>
+        <v>6398252</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,17 +985,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,83 +1009,69 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131734488</t>
+          <t>https://artportalen.se/Sighting/119266053</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105920013</v>
+        <v>131734488</v>
       </c>
       <c r="B5" t="n">
-        <v>91867</v>
+        <v>96410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5445</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 765, Ankarsrums säteri, Sm</t>
+          <t>Kärren Sydväst, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579189</v>
+        <v>579272</v>
       </c>
       <c r="R5" t="n">
-        <v>6398315</v>
+        <v>6398140</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,12 +1098,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,31 +1117,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105920013</t>
+          <t>https://artportalen.se/Sighting/131734488</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105920045</v>
+        <v>105920013</v>
       </c>
       <c r="B6" t="n">
         <v>91867</v>
@@ -1173,7 +1174,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1189,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579174</v>
+        <v>579189</v>
       </c>
       <c r="R6" t="n">
-        <v>6398184</v>
+        <v>6398315</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1251,13 +1252,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105920045</t>
+          <t>https://artportalen.se/Sighting/105920013</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118564416</v>
+        <v>105920045</v>
       </c>
       <c r="B7" t="n">
         <v>91867</v>
@@ -1287,7 +1288,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1299,14 +1300,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 27737, Ankarsrums säteri, Sm</t>
+          <t>A 765, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579165</v>
+        <v>579174</v>
       </c>
       <c r="R7" t="n">
-        <v>6398368</v>
+        <v>6398184</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,12 +1334,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,16 +1366,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118564416</t>
+          <t>https://artportalen.se/Sighting/105920045</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131732492</v>
+        <v>118564416</v>
       </c>
       <c r="B8" t="n">
-        <v>91932</v>
+        <v>91867</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,17 +1400,28 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kammarbogöl Nord, Sm</t>
+          <t>A 27737, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579297</v>
+        <v>579165</v>
       </c>
       <c r="R8" t="n">
-        <v>6398143</v>
+        <v>6398368</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,12 +1448,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,72 +1462,69 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131732492</t>
+          <t>https://artportalen.se/Sighting/118564416</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131737000</v>
+        <v>131732492</v>
       </c>
       <c r="B9" t="n">
-        <v>75340</v>
+        <v>91932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6428</v>
+        <v>5445</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kammartorp Väst, Sm</t>
+          <t>Kammarbogöl Nord, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579356</v>
+        <v>579297</v>
       </c>
       <c r="R9" t="n">
-        <v>6398090</v>
+        <v>6398143</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,11 +1559,6 @@
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På ek</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1582,59 +1586,65 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131737000</t>
+          <t>https://artportalen.se/Sighting/131732492</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118608293</v>
+        <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>57950</v>
+        <v>92075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5445</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kärren, Kärren, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579256</v>
+        <v>579205</v>
       </c>
       <c r="R10" t="n">
-        <v>6398133</v>
+        <v>6398277</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1658,22 +1668,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,33 +1682,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118608293</t>
+          <t>https://artportalen.se/Sighting/137091314</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118608477</v>
+        <v>131737000</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>75340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,42 +1717,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+          <t>Kammartorp Väst, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579312</v>
+        <v>579356</v>
       </c>
       <c r="R11" t="n">
-        <v>6398154</v>
+        <v>6398090</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,22 +1771,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På ek</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,24 +1796,28 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118608477</t>
+          <t>https://artportalen.se/Sighting/131737000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119624115</v>
+        <v>118608293</v>
       </c>
       <c r="B12" t="n">
         <v>57950</v>
@@ -1851,27 +1846,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>Kärren, Kärren, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579298</v>
+        <v>579256</v>
       </c>
       <c r="R12" t="n">
-        <v>6398158</v>
+        <v>6398133</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,17 +1887,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>I asp</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,27 +1917,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624115</t>
+          <t>https://artportalen.se/Sighting/118608293</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118564572</v>
+        <v>118608477</v>
       </c>
       <c r="B13" t="n">
-        <v>97986</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,45 +1945,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 27737, Ankarsrums säteri, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579210</v>
+        <v>579312</v>
       </c>
       <c r="R13" t="n">
-        <v>6398292</v>
+        <v>6398154</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2010,12 +2004,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,34 +2028,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118564572</t>
+          <t>https://artportalen.se/Sighting/118608477</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131733125</v>
+        <v>119624115</v>
       </c>
       <c r="B14" t="n">
-        <v>101403</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,34 +2062,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kammartorp Väst, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579346</v>
+        <v>579298</v>
       </c>
       <c r="R14" t="n">
-        <v>6398047</v>
+        <v>6398158</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,12 +2124,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>I asp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,20 +2149,345 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119624115</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137073518</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>579351</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6398114</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073518</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118564572</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 27737, Ankarsrums säteri, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>579210</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6398292</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118564572</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131733125</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kammartorp Väst, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>579346</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6398047</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
+      <c r="AY17" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131733125</t>
         </is>
@@ -2167,6 +2508,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92075</v>
+        <v>92076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92076</v>
+        <v>92082</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92082</v>
+        <v>92086</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92086</v>
+        <v>92088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>137073518</v>
       </c>
       <c r="B15" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>137073518</v>
       </c>
       <c r="B15" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1706,45 +1706,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131737000</v>
+        <v>137269077</v>
       </c>
       <c r="B11" t="n">
-        <v>75340</v>
+        <v>92106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6428</v>
+        <v>5445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kammartorp Väst, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579356</v>
+        <v>579185</v>
       </c>
       <c r="R11" t="n">
-        <v>6398090</v>
+        <v>6398300</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,17 +1782,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På ek</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,37 +1796,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131737000</t>
+          <t>https://artportalen.se/Sighting/137269077</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118608293</v>
+        <v>131737000</v>
       </c>
       <c r="B12" t="n">
-        <v>57950</v>
+        <v>75340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,42 +1831,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kärren, Kärren, Sm</t>
+          <t>Kammartorp Väst, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579256</v>
+        <v>579356</v>
       </c>
       <c r="R12" t="n">
-        <v>6398133</v>
+        <v>6398090</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1887,22 +1885,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På ek</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,24 +1910,28 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118608293</t>
+          <t>https://artportalen.se/Sighting/131737000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118608477</v>
+        <v>118608293</v>
       </c>
       <c r="B13" t="n">
         <v>57950</v>
@@ -1970,14 +1967,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+          <t>Kärren, Kärren, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579312</v>
+        <v>579256</v>
       </c>
       <c r="R13" t="n">
-        <v>6398154</v>
+        <v>6398133</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2009,7 +2006,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,7 +2016,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,13 +2042,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118608477</t>
+          <t>https://artportalen.se/Sighting/118608293</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119624115</v>
+        <v>118608477</v>
       </c>
       <c r="B14" t="n">
         <v>57950</v>
@@ -2080,27 +2077,24 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579298</v>
+        <v>579312</v>
       </c>
       <c r="R14" t="n">
-        <v>6398158</v>
+        <v>6398154</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,17 +2118,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>I asp</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,27 +2148,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624115</t>
+          <t>https://artportalen.se/Sighting/118608477</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137073518</v>
+        <v>119624115</v>
       </c>
       <c r="B15" t="n">
-        <v>58179</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,16 +2176,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103023</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2195,19 +2194,27 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579351</v>
+        <v>579298</v>
       </c>
       <c r="R15" t="n">
-        <v>6398114</v>
+        <v>6398158</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2231,22 +2238,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I asp</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,73 +2263,73 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073518</t>
+          <t>https://artportalen.se/Sighting/119624115</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118564572</v>
+        <v>137269124</v>
       </c>
       <c r="B16" t="n">
-        <v>97986</v>
+        <v>58184</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 27737, Ankarsrums säteri, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579210</v>
+        <v>579207</v>
       </c>
       <c r="R16" t="n">
-        <v>6398292</v>
+        <v>6398281</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2351,12 +2353,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,7 +2367,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2383,16 +2384,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118564572</t>
+          <t>https://artportalen.se/Sighting/137269124</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131733125</v>
+        <v>137073518</v>
       </c>
       <c r="B17" t="n">
-        <v>101403</v>
+        <v>58179</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2400,37 +2401,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>103023</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kammartorp Väst, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579346</v>
+        <v>579351</v>
       </c>
       <c r="R17" t="n">
-        <v>6398047</v>
+        <v>6398114</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2454,12 +2455,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,20 +2485,233 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073518</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118564572</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 27737, Ankarsrums säteri, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>579210</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6398292</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118564572</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131733125</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kammartorp Väst, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>579346</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6398047</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
+      <c r="AY19" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131733125</t>
         </is>
@@ -2511,6 +2735,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92103</v>
+        <v>92106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92106</v>
+        <v>92116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>137269077</v>
       </c>
       <c r="B11" t="n">
-        <v>92106</v>
+        <v>92116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137269124</v>
       </c>
       <c r="B16" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>137073518</v>
       </c>
       <c r="B17" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92116</v>
+        <v>92117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>137269077</v>
       </c>
       <c r="B11" t="n">
-        <v>92116</v>
+        <v>92117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1931,27 +1931,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118608293</v>
+        <v>137342625</v>
       </c>
       <c r="B13" t="n">
-        <v>57950</v>
+        <v>58046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1960,24 +1960,20 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kärren, Kärren, Sm</t>
+          <t>Kärren, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579256</v>
+        <v>579175</v>
       </c>
       <c r="R13" t="n">
-        <v>6398133</v>
+        <v>6398194</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2001,22 +1997,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,24 +2027,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118608293</t>
+          <t>https://artportalen.se/Sighting/137342625</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118608477</v>
+        <v>118608293</v>
       </c>
       <c r="B14" t="n">
         <v>57950</v>
@@ -2084,14 +2080,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+          <t>Kärren, Kärren, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579312</v>
+        <v>579256</v>
       </c>
       <c r="R14" t="n">
-        <v>6398154</v>
+        <v>6398133</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2123,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2133,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,13 +2155,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118608477</t>
+          <t>https://artportalen.se/Sighting/118608293</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119624115</v>
+        <v>118608477</v>
       </c>
       <c r="B15" t="n">
         <v>57950</v>
@@ -2194,27 +2190,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579298</v>
+        <v>579312</v>
       </c>
       <c r="R15" t="n">
-        <v>6398158</v>
+        <v>6398154</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2238,17 +2231,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>I asp</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,73 +2261,73 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624115</t>
+          <t>https://artportalen.se/Sighting/118608477</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137269124</v>
+        <v>119624115</v>
       </c>
       <c r="B16" t="n">
-        <v>58194</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 27727, Stormandebo, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579207</v>
+        <v>579298</v>
       </c>
       <c r="R16" t="n">
-        <v>6398281</v>
+        <v>6398158</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2353,12 +2351,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>I asp</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,54 +2387,62 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137269124</t>
+          <t>https://artportalen.se/Sighting/119624115</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137073518</v>
+        <v>137269124</v>
       </c>
       <c r="B17" t="n">
-        <v>58189</v>
+        <v>58194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579351</v>
+        <v>579207</v>
       </c>
       <c r="R17" t="n">
-        <v>6398114</v>
+        <v>6398281</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2455,22 +2466,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,27 +2486,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073518</t>
+          <t>https://artportalen.se/Sighting/137269124</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118564572</v>
+        <v>137073518</v>
       </c>
       <c r="B18" t="n">
-        <v>97986</v>
+        <v>58189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2513,45 +2514,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221946</v>
+        <v>103023</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 27737, Ankarsrums säteri, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579210</v>
+        <v>579351</v>
       </c>
       <c r="R18" t="n">
-        <v>6398292</v>
+        <v>6398114</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2575,12 +2568,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,34 +2592,33 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118564572</t>
+          <t>https://artportalen.se/Sighting/137073518</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131733125</v>
+        <v>118564572</v>
       </c>
       <c r="B19" t="n">
-        <v>101403</v>
+        <v>97986</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,34 +2626,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kammartorp Väst, Sm</t>
+          <t>A 27737, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579346</v>
+        <v>579210</v>
       </c>
       <c r="R19" t="n">
-        <v>6398047</v>
+        <v>6398292</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2678,12 +2688,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2692,26 +2702,129 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118564572</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131733125</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kammartorp Väst, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>579346</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6398047</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
+      <c r="AY20" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131733125</t>
         </is>
@@ -2737,6 +2850,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92117</v>
+        <v>92120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>137269077</v>
       </c>
       <c r="B11" t="n">
-        <v>92117</v>
+        <v>92120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137342625</v>
       </c>
       <c r="B13" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137269124</v>
       </c>
       <c r="B17" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>137073518</v>
       </c>
       <c r="B18" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92120</v>
+        <v>92122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>137269077</v>
       </c>
       <c r="B11" t="n">
-        <v>92120</v>
+        <v>92122</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92122</v>
+        <v>92127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>137269077</v>
       </c>
       <c r="B11" t="n">
-        <v>92122</v>
+        <v>92127</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137342625</v>
       </c>
       <c r="B13" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137269124</v>
       </c>
       <c r="B17" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>137073518</v>
       </c>
       <c r="B18" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92127</v>
+        <v>92139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>137269077</v>
       </c>
       <c r="B11" t="n">
-        <v>92127</v>
+        <v>92139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92139</v>
+        <v>92140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>137269077</v>
       </c>
       <c r="B11" t="n">
-        <v>92139</v>
+        <v>92140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92140</v>
+        <v>92143</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>137269077</v>
       </c>
       <c r="B11" t="n">
-        <v>92140</v>
+        <v>92143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137091314</v>
       </c>
       <c r="B10" t="n">
-        <v>92143</v>
+        <v>92147</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>137269077</v>
       </c>
       <c r="B11" t="n">
-        <v>92143</v>
+        <v>92147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137342625</v>
       </c>
       <c r="B13" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137269124</v>
       </c>
       <c r="B17" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>137073518</v>
       </c>
       <c r="B18" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
